--- a/static/standards-correlations/Arizona_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Arizona_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$31</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Arizona CS Standards, October 2018</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Arizona CS Standards, October 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -785,7 +786,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) shows a password exposed over HTTP. Discovery Systems 10 covers phishing.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) shows a password exposed over HTTP. Introductory Systems 10 covers phishing.</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1479,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Unit 5.3 teaches version control, repositories, and commits directly. Discovery Systems 13 and 14 assign team roles and manage a project timeline. Botball Explorer is team-based by design.</t>
+          <t>Unit 5.3 teaches version control, repositories, and commits directly. Introductory Systems 13 and 14 assign team roles and manage a project timeline. Botball Explorer is team-based by design.</t>
         </is>
       </c>
     </row>
@@ -1876,6 +1877,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1920,7 +1922,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1934,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2032,6 +2034,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -2049,7 +2053,7 @@
 LINEAGE: Arizona's standards draw on the CSTA Interim K-12 CS Standards (rev. 2016), the K-12 CS Framework, and draft standards from Nevada and Wisconsin. Identifiers are Arizona's own and differ from CSTA 2017.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 An earlier revision of this file scored lab FRONT MATTER ONLY (headings, descriptions, concept tags, objectives) and materially undercounted coverage. Those figures are superseded.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?' in the labs), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension carrying the evidence, so a reviewer can verify placement and decide whether optional work counts for their purposes.</t>
         </is>
